--- a/spravki/spravka_rnntd_summary_2026-09-30.xlsx
+++ b/spravki/spravka_rnntd_summary_2026-09-30.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>64.9 млрд ₸</t>
+          <t>65.7 млрд ₸</t>
         </is>
       </c>
     </row>
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -641,54 +641,54 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>859</v>
+        <v>938</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Здравоохранение</t>
+          <t>Не указано</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Обрабатывающая промышленность</t>
+          <t>Здравоохранение</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -697,40 +697,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>218</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Не указано</t>
+          <t>Обрабатывающая промышленность</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -740,11 +740,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>91</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
@@ -754,11 +754,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -787,11 +787,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -820,11 +820,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -949,11 +949,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>705</v>
+        <v>754</v>
       </c>
     </row>
     <row r="29">
@@ -963,16 +963,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -982,77 +982,77 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>394</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Астана</t>
+          <t>Не указано</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>229</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Не указано</t>
+          <t>Астана</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>91</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32">
@@ -1062,16 +1062,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1085,26 +1085,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Карагандинская область</t>
+          <t>Туркестанская область</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1114,30 +1114,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Туркестанская область</t>
+          <t>Карагандинская область</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35">
@@ -1161,11 +1161,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1190,7 +1190,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 407. Сформировано 16.10.2026.</t>
+          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 475. Сформировано 16.10.2026.</t>
         </is>
       </c>
     </row>
